--- a/cet4/result/86_穿越女帝_凤倾天下的权谋/86_穿越女帝_凤倾天下的权谋_学习版.xlsx
+++ b/cet4/result/86_穿越女帝_凤倾天下的权谋/86_穿越女帝_凤倾天下的权谋_学习版.xlsx
@@ -399,710 +399,710 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>manager</v>
       </c>
       <c r="B2" t="str">
-        <v>manager</v>
+        <v>/ˈmænɪdʒər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>经理</v>
       </c>
-      <c r="D2" t="str">
-        <v>manager(经理)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>quote</v>
       </c>
       <c r="B3" t="str">
-        <v>quote</v>
+        <v>/kwoʊt/</v>
       </c>
       <c r="C3" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>引用</v>
       </c>
-      <c r="D3" t="str">
-        <v>quote(引用)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>hurt</v>
       </c>
       <c r="B4" t="str">
-        <v>hurt</v>
+        <v>/hɜːrt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D4" t="str">
         <v>伤害</v>
       </c>
-      <c r="D4" t="str">
-        <v>hurt(伤害)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>democratic</v>
       </c>
       <c r="B5" t="str">
-        <v>democratic</v>
+        <v>/ˌdeməˈkrætɪk/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>民主的</v>
       </c>
-      <c r="D5" t="str">
-        <v>democratic(民主的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>definition</v>
       </c>
       <c r="B6" t="str">
-        <v>definition</v>
+        <v>/ˌdefɪˈnɪʃn/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>定义</v>
       </c>
-      <c r="D6" t="str">
-        <v>definition(定义)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>shake</v>
       </c>
       <c r="B7" t="str">
-        <v>shake</v>
+        <v>/ʃeɪk/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>动摇</v>
       </c>
-      <c r="D7" t="str">
-        <v>shake(动摇)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>truth</v>
       </c>
       <c r="B8" t="str">
-        <v>truth</v>
+        <v>/truːθ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>真相</v>
       </c>
-      <c r="D8" t="str">
-        <v>truth(真相)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>marry</v>
       </c>
       <c r="B9" t="str">
-        <v>marry</v>
+        <v>/ˈmæri/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>娶</v>
       </c>
-      <c r="D9" t="str">
-        <v>marry(娶)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>effort</v>
       </c>
       <c r="B10" t="str">
-        <v>effort</v>
+        <v>/ˈefərt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>努力</v>
       </c>
-      <c r="D10" t="str">
-        <v>effort(努力)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>China</v>
       </c>
       <c r="B11" t="str">
-        <v>China</v>
+        <v>/ˈtʃaɪnə/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>中国</v>
       </c>
-      <c r="D11" t="str">
-        <v>China(中国)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>bus</v>
       </c>
       <c r="B12" t="str">
-        <v>bus</v>
+        <v>/bʌs/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>马车</v>
       </c>
-      <c r="D12" t="str">
-        <v>bus(马车)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>sand</v>
       </c>
       <c r="B13" t="str">
-        <v>sand</v>
+        <v>/sænd/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D13" t="str">
         <v>沙地</v>
       </c>
-      <c r="D13" t="str">
-        <v>sand(沙地)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>arouse</v>
       </c>
       <c r="B14" t="str">
-        <v>arouse</v>
+        <v>/əˈraʊz/</v>
       </c>
       <c r="C14" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>唤起</v>
       </c>
-      <c r="D14" t="str">
-        <v>arouse(唤起)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>shortcoming</v>
       </c>
       <c r="B15" t="str">
-        <v>shortcoming</v>
+        <v>/ˈʃɔːrtkʌmɪŋ/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>缺点</v>
       </c>
-      <c r="D15" t="str">
-        <v>shortcoming(缺点)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>enforce</v>
       </c>
       <c r="B16" t="str">
-        <v>enforce</v>
+        <v>/ɪnˈfɔːrs/</v>
       </c>
       <c r="C16" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D16" t="str">
         <v>执行</v>
       </c>
-      <c r="D16" t="str">
-        <v>enforce(执行)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>flock</v>
       </c>
       <c r="B17" t="str">
-        <v>flock</v>
+        <v>/flɑːk/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>聚集</v>
       </c>
-      <c r="D17" t="str">
-        <v>flock(聚集)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>tip</v>
       </c>
       <c r="B18" t="str">
-        <v>tip</v>
+        <v>/tɪp/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>建议</v>
       </c>
-      <c r="D18" t="str">
-        <v>tip(建议)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>knock</v>
       </c>
       <c r="B19" t="str">
-        <v>knock</v>
+        <v>/nɑːk/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>敲</v>
       </c>
-      <c r="D19" t="str">
-        <v>knock(敲)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>whistle</v>
       </c>
       <c r="B20" t="str">
-        <v>whistle</v>
+        <v>/ˈwɪsl/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D20" t="str">
         <v>口哨</v>
       </c>
-      <c r="D20" t="str">
-        <v>whistle(口哨)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>salary</v>
       </c>
       <c r="B21" t="str">
-        <v>salary</v>
+        <v>/ˈsæləri/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D21" t="str">
         <v>薪水</v>
       </c>
-      <c r="D21" t="str">
-        <v>salary(薪水)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>whisper</v>
       </c>
       <c r="B22" t="str">
-        <v>whisper</v>
+        <v>/ˈwɪspər/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D22" t="str">
         <v>耳语</v>
       </c>
-      <c r="D22" t="str">
-        <v>whisper(耳语)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>research</v>
       </c>
       <c r="B23" t="str">
-        <v>research</v>
+        <v>/rɪ'sɜːtʃ/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>研究</v>
       </c>
-      <c r="D23" t="str">
-        <v>research(研究)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>close</v>
       </c>
       <c r="B24" t="str">
-        <v>close</v>
+        <v>/kloʊz; kloʊs/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>亲近</v>
       </c>
-      <c r="D24" t="str">
-        <v>close(亲近)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>match</v>
       </c>
       <c r="B25" t="str">
-        <v>match</v>
+        <v>/mætʃ/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D25" t="str">
         <v>比赛</v>
       </c>
-      <c r="D25" t="str">
-        <v>match(比赛)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>protection</v>
       </c>
       <c r="B26" t="str">
-        <v>protection</v>
+        <v>/prəˈtekʃn/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>保护</v>
       </c>
-      <c r="D26" t="str">
-        <v>protection(保护)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>seven</v>
       </c>
       <c r="B27" t="str">
-        <v>seven</v>
+        <v>/ˈsevn/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D27" t="str">
         <v>七</v>
       </c>
-      <c r="D27" t="str">
-        <v>seven(七)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>crew</v>
       </c>
       <c r="B28" t="str">
-        <v>crew</v>
+        <v>/kruː/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D28" t="str">
         <v>成员</v>
       </c>
-      <c r="D28" t="str">
-        <v>crew(成员)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>installation</v>
       </c>
       <c r="B29" t="str">
-        <v>installation</v>
+        <v>/ˌɪnstəˈleɪʃn/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>安装</v>
       </c>
-      <c r="D29" t="str">
-        <v>installation(安装)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>it</v>
       </c>
       <c r="B30" t="str">
-        <v>it</v>
+        <v>/ɪt/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D30" t="str">
         <v>这</v>
       </c>
-      <c r="D30" t="str">
-        <v>it(这)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>guilty</v>
       </c>
       <c r="B31" t="str">
-        <v>guilty</v>
+        <v>/ˈɡɪlti/</v>
       </c>
       <c r="C31" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D31" t="str">
         <v>内疚</v>
       </c>
-      <c r="D31" t="str">
-        <v>guilty(内疚)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>majority</v>
       </c>
       <c r="B32" t="str">
-        <v>majority</v>
+        <v>/məˈdʒɔːrəti/</v>
       </c>
       <c r="C32" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>多数</v>
       </c>
-      <c r="D32" t="str">
-        <v>majority(多数)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>friendly</v>
       </c>
       <c r="B33" t="str">
-        <v>friendly</v>
+        <v>/ˈfrendli/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>友好的</v>
       </c>
-      <c r="D33" t="str">
-        <v>friendly(友好的)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>feel</v>
       </c>
       <c r="B34" t="str">
-        <v>feel</v>
+        <v>/fiːl/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D34" t="str">
         <v>感受到</v>
       </c>
-      <c r="D34" t="str">
-        <v>feel(感受到)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>Russian</v>
       </c>
       <c r="B35" t="str">
-        <v>Russian</v>
+        <v>/ˈrʌʃn/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D35" t="str">
         <v>俄国</v>
       </c>
-      <c r="D35" t="str">
-        <v>Russian(俄国)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>opposite</v>
       </c>
       <c r="B36" t="str">
-        <v>opposite</v>
+        <v>/ˈɑːpəzɪt/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./v./adj./adv./prep.</v>
+      </c>
+      <c r="D36" t="str">
         <v>对面</v>
       </c>
-      <c r="D36" t="str">
-        <v>opposite(对面)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>crow</v>
       </c>
       <c r="B37" t="str">
-        <v>crow</v>
+        <v>/kroʊ/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D37" t="str">
         <v>乌鸦</v>
       </c>
-      <c r="D37" t="str">
-        <v>crow(乌鸦)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>risk</v>
       </c>
       <c r="B38" t="str">
-        <v>risk</v>
+        <v>/rɪsk/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D38" t="str">
         <v>风险</v>
       </c>
-      <c r="D38" t="str">
-        <v>risk(风险)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>afford</v>
       </c>
       <c r="B39" t="str">
-        <v>afford</v>
+        <v>/əˈfɔːrd/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D39" t="str">
         <v>承受得起</v>
       </c>
-      <c r="D39" t="str">
-        <v>afford(承受得起)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>exception</v>
       </c>
       <c r="B40" t="str">
-        <v>exception</v>
+        <v>/ɪkˈsepʃn/</v>
       </c>
       <c r="C40" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>例外</v>
       </c>
-      <c r="D40" t="str">
-        <v>exception(例外)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>sweep</v>
       </c>
       <c r="B41" t="str">
-        <v>sweep</v>
+        <v>/swiːp/</v>
       </c>
       <c r="C41" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D41" t="str">
         <v>席卷</v>
       </c>
-      <c r="D41" t="str">
-        <v>sweep(席卷)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>obey</v>
       </c>
       <c r="B42" t="str">
-        <v>obey</v>
+        <v>/əˈbeɪ/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>服从</v>
       </c>
-      <c r="D42" t="str">
-        <v>obey(服从)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>map</v>
       </c>
       <c r="B43" t="str">
-        <v>map</v>
+        <v>/mæp/</v>
       </c>
       <c r="C43" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D43" t="str">
         <v>地图</v>
       </c>
-      <c r="D43" t="str">
-        <v>map(地图)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>responsibility</v>
       </c>
       <c r="B44" t="str">
-        <v>responsibility</v>
+        <v>/rɪˌspɑːnsəˈbɪləti/</v>
       </c>
       <c r="C44" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>责任</v>
       </c>
-      <c r="D44" t="str">
-        <v>responsibility(责任)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>such</v>
       </c>
       <c r="B45" t="str">
-        <v>such</v>
+        <v>/sʌtʃ/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./adj./pron.</v>
+      </c>
+      <c r="D45" t="str">
         <v>如此</v>
       </c>
-      <c r="D45" t="str">
-        <v>such(如此)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>tense</v>
       </c>
       <c r="B46" t="str">
-        <v>tense</v>
+        <v>/tens/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D46" t="str">
         <v>紧张</v>
       </c>
-      <c r="D46" t="str">
-        <v>tense(紧张)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>whom</v>
       </c>
       <c r="B47" t="str">
-        <v>whom</v>
+        <v>/huːm/</v>
       </c>
       <c r="C47" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D47" t="str">
         <v>谁</v>
       </c>
-      <c r="D47" t="str">
-        <v>whom(谁)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>thunder</v>
       </c>
       <c r="B48" t="str">
-        <v>thunder</v>
+        <v>/ˈθʌndər/</v>
       </c>
       <c r="C48" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D48" t="str">
         <v>雷声</v>
       </c>
-      <c r="D48" t="str">
-        <v>thunder(雷声)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>deliver</v>
       </c>
       <c r="B49" t="str">
-        <v>deliver</v>
+        <v>/dɪˈlɪvər/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D49" t="str">
         <v>实现</v>
       </c>
-      <c r="D49" t="str">
-        <v>deliver(实现)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>organize</v>
       </c>
       <c r="B50" t="str">
-        <v>organize</v>
+        <v>/ˈɔːrɡənaɪz/</v>
       </c>
       <c r="C50" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D50" t="str">
         <v>组织</v>
-      </c>
-      <c r="D50" t="str">
-        <v>organize(组织)📢</v>
       </c>
     </row>
   </sheetData>
